--- a/Topic Relevant Comments - Nigeria/Banky Wellington/My Story Journey Through Hope and Faith.xlsx
+++ b/Topic Relevant Comments - Nigeria/Banky Wellington/My Story Journey Through Hope and Faith.xlsx
@@ -55,6 +55,9 @@
     <t>Banky, this message will outlive you. You don't have an idea what you have just done with this. Thanks for yielding to the leading of the spirit of God by sharing your story as a testimony. The good thing is that you did not share your experience as the testimony, rather the faith in the word of God- that's the testimony!</t>
   </si>
   <si>
+    <t>My faith is lifted up</t>
+  </si>
+  <si>
     <t>God give me the grace to have in totality the faith and trust in you</t>
   </si>
   <si>
@@ -109,12 +112,12 @@
     <t>To be honest ur story in press me and I learned a lot from ur story, i was worried but after watching this video i have confidence thanks for sharing bros.</t>
   </si>
   <si>
+    <t>Omdss I can image your experience working (Life is a Journey) All we need is to have faith and believe the plans God has for us</t>
+  </si>
+  <si>
     <t>I Loved every moment of this! Bless God for the Testimonies: He's Faithful</t>
   </si>
   <si>
-    <t>Omdss I can image your experience working (Life is a Journey) All we need is to have faith and believe the plans God has for us</t>
-  </si>
-  <si>
     <t>God is faithful, This is a powerful message for young ppl. Roman wasn't built in a day... God richly bless you Banky</t>
   </si>
   <si>
@@ -244,6 +247,9 @@
     <t>I'm partially in a lost place in my life and watching this video before and after church just lit a spark of faith in my life and i know my God knows what i want and I believe he'll do it..Thank you so much for this Banky</t>
   </si>
   <si>
+    <t>Am so happy for you and your wife.</t>
+  </si>
+  <si>
     <t>My son, I love you already, you're a man of God in the making, God bless you and your family immensely. I admire your faith at 60 I have learned a lot from you. Once again God bless you immensely in Jesus Mighty Name.</t>
   </si>
   <si>
@@ -259,9 +265,6 @@
     <t>@pastorrobertmorris8717 if you don't want your children to be candidates of that motherless home, DESIST FROM THIS FRAUD!!!</t>
   </si>
   <si>
-    <t>A very inspiring story. God bless you more Banky. You are a blessed man</t>
-  </si>
-  <si>
     <t>Thanks for Mr Banky W for your amazing testimony and for inspiring me. May God continues to bless you and your Wife and your kids in Jesus name amen.</t>
   </si>
   <si>
@@ -328,6 +331,9 @@
     <t>Gosh I'm just seeing this and it couldn't have been more timely. Banky,I give God glory for you! you are indeed a man of Faith. God bless you brother,keep shining your light!!!!!!</t>
   </si>
   <si>
+    <t>I believe my brother Banky is a Pastor in the making, you only have to be consistent with the work of God., i have been so blessed by your ministration . God bless you mightily man of God, you are a light that shines in darkness, keep shining and manifesting the glory of our God.</t>
+  </si>
+  <si>
     <t>Listening to you, I feel encouraged that God is with us, walking and working with us, even when we don't know.</t>
   </si>
   <si>
@@ -337,9 +343,6 @@
     <t>Couldn't go to church today, but I chanced on this video and it has blessed and inspired me. Reinstalling hope and reestablishing Faith, thank you Banky.</t>
   </si>
   <si>
-    <t>I believe my brother Banky is a Pastor in the making, you only have to be consistent with the work of God., i have been so blessed by your ministration . God bless you mightily man of God, you are a light that shines in darkness, keep shining and manifesting the glory of our God.</t>
-  </si>
-  <si>
     <t>Beloved, I don't know you in person but God knows you. God ministered to me in a revelation when I was on your profile to see things around you,I saw blessings but spiritual attacks holding onto them,in prayers,i saw a woman in the realm of the spirit monitoring and plotting delay in your life, with an evil mirror, and with a motive to destroy. But as I speak to you now her time is up, Render hand of favour with Anything you can afford or give to these motherless foundation (Godstime MOTHERLESS FOUNDATION) in kebbi state nigeria before 2DAYS with faith, as I Rise my hands towards heaven and pray for you they shall serve as point of contact wherever you are, you will receive double portion of grace to excel and total restoration of breakthrough in your life and in the life of your family. Ask for their acct details and help them call the MD in charge of the orphanage to get their details on (WhatsApp or call them now on (+2349150343459 tell him I sent an you. For it is not by might nor by in power but of the spirit saith the lord (zechariah 4:6). You shall testify to the Glory of God in your life. God bless.........................</t>
   </si>
   <si>
@@ -490,6 +493,9 @@
     <t>A great testimony. Very inspiring and so soul lifting. Olubankole keep the fire burning. You are a blessing and a role model to both your generation as well as our youths and young adults</t>
   </si>
   <si>
+    <t>Very inspiring ,thank you Banky for sharing this testimony with all and sundry.</t>
+  </si>
+  <si>
     <t>Thanks for sharing this your story,very inspiring,God bless you,your home and your beautiful family ❤️❤️</t>
   </si>
   <si>
@@ -589,15 +595,15 @@
     <t>This is inspiring, I activate God's uncommon favour and grace over every aspect of my life and family.</t>
   </si>
   <si>
+    <t>Thanks so much for sharing your journey through life. It's soul lifting, God bless you Banky W.</t>
+  </si>
+  <si>
     <t>Really... inspiring. I mean I was so.... blessed. Olubankole and Adesuwa we love you. Your best days are yet to come. keep on keeping on in God. You are role models. God bless you real good.</t>
   </si>
   <si>
     <t>This has given me strength to carry on with life thank God for using u to touch lives</t>
   </si>
   <si>
-    <t>Thanks so much for sharing your journey through life. It's soul lifting, God bless you Banky W.</t>
-  </si>
-  <si>
     <t>Beautiful, this is so relatable. God bless him and his family. Such a beautiful example.</t>
   </si>
   <si>
@@ -611,12 +617,6 @@
   </si>
   <si>
     <t>Wow Banky W, this was really good. Thanks for posting this and allowing God to use you as a vessel to give this testimony. God bless you</t>
-  </si>
-  <si>
-    <t>Joseph Olubankole Wellington...our own version of the Bible story of Joseph. Hmmm...</t>
-  </si>
-  <si>
-    <t>I am bless if God bless you and changing your story the LORD will bless me and change my life and story to a higher positionsthe LORD will do that also for me and my family</t>
   </si>
 </sst>
 </file>
